--- a/astro-site/public/dl/kit-escandallos/04-cocktails-bebidas.xlsx
+++ b/astro-site/public/dl/kit-escandallos/04-cocktails-bebidas.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gin Tonic Premium" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mojito Clásico" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Margarita" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Aperol Spritz" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gin Tonic Premium" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mojito Clásico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margarita" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aperol Spritz" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Gin Tonic Premium'!$A$1:$I$25</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Mojito Clásico'!$A$1:$I$25</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Margarita'!$A$1:$I$24</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Aperol Spritz'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Gin Tonic Premium'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Gin Tonic Premium'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mojito Clásico'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Mojito Clásico'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Margarita'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Margarita'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Aperol Spritz'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Aperol Spritz'!$A$1:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,9 +30,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.000" numFmtId="165"/>
-    <numFmt formatCode="0.0%" numFmtId="166"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -173,7 +177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -353,112 +357,172 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFD700"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="51">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="3" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="3" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="5" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="12" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="13" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="6" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="7" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="15" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="16" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="17" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -818,15 +882,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -848,6 +913,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -896,10 +962,19 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -907,7 +982,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -916,23 +1000,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -955,7 +1039,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1038,11 +1122,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.05102040816326531</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>1.4285714285714286</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1079,11 +1163,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1120,11 +1204,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.024999999999999998</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.06249999999999999</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1161,11 +1245,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.011363636363636364</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.017045454545454544</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1207,11 +1291,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.002105263157894737</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.06315789473684211</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1248,11 +1332,11 @@
       </c>
       <c r="H10" s="20">
         <f>E10/(1-G10)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="I10" s="21">
         <f>H10*D10</f>
-        <v/>
+        <v>0.075</v>
       </c>
       <c r="K10" s="22" t="n"/>
       <c r="L10" s="23" t="n"/>
@@ -1362,9 +1446,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
       <c r="I17" s="36">
         <f>SUM(I5:I15)</f>
-        <v/>
+        <v>3.146274777853726</v>
       </c>
     </row>
     <row r="18">
@@ -1373,12 +1464,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
       <c r="H18" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" s="38">
         <f>I17*H18</f>
-        <v/>
+        <v>0.3146274777853726</v>
       </c>
     </row>
     <row r="19">
@@ -1387,9 +1484,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="50" t="n"/>
       <c r="I19" s="40">
         <f>I17+I18</f>
-        <v/>
+        <v>3.4609022556390983</v>
       </c>
     </row>
     <row r="20"/>
@@ -1399,6 +1503,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="50" t="n"/>
       <c r="H21" s="42" t="n">
         <v>0.2</v>
       </c>
@@ -1409,9 +1519,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
       <c r="I22" s="44">
         <f>I19/H21</f>
-        <v/>
+        <v>17.30451127819549</v>
       </c>
     </row>
     <row r="23">
@@ -1420,9 +1537,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="46">
         <f>I22*1.10</f>
-        <v/>
+        <v>19.03496240601504</v>
       </c>
     </row>
     <row r="24">
@@ -1431,9 +1555,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="38">
         <f>I22-I19</f>
-        <v/>
+        <v>13.843609022556393</v>
       </c>
     </row>
     <row r="25">
@@ -1442,16 +1573,22 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="50" t="n"/>
       <c r="I25" s="47">
         <f>I24/I22</f>
-        <v/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:G18"/>
@@ -1461,18 +1598,27 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1481,23 +1627,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1520,7 +1666,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1603,11 +1749,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.061224489795918366</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>0.9183673469387755</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1644,11 +1790,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.0375</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.16874999999999998</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1685,11 +1831,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.625</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1726,11 +1872,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.015306122448979591</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.01836734693877551</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1772,11 +1918,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.048</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1813,11 +1959,11 @@
       </c>
       <c r="H10" s="20">
         <f>E10/(1-G10)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="I10" s="21">
         <f>H10*D10</f>
-        <v/>
+        <v>0.075</v>
       </c>
       <c r="K10" s="22" t="n"/>
       <c r="L10" s="23" t="n"/>
@@ -1927,9 +2073,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
       <c r="I17" s="36">
         <f>SUM(I5:I15)</f>
-        <v/>
+        <v>1.978484693877551</v>
       </c>
     </row>
     <row r="18">
@@ -1938,12 +2091,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
       <c r="H18" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" s="38">
         <f>I17*H18</f>
-        <v/>
+        <v>0.19784846938775513</v>
       </c>
     </row>
     <row r="19">
@@ -1952,9 +2111,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="50" t="n"/>
       <c r="I19" s="40">
         <f>I17+I18</f>
-        <v/>
+        <v>2.1763331632653062</v>
       </c>
     </row>
     <row r="20"/>
@@ -1964,6 +2130,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="50" t="n"/>
       <c r="H21" s="42" t="n">
         <v>0.2</v>
       </c>
@@ -1974,9 +2146,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
       <c r="I22" s="44">
         <f>I19/H21</f>
-        <v/>
+        <v>10.88166581632653</v>
       </c>
     </row>
     <row r="23">
@@ -1985,9 +2164,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="46">
         <f>I22*1.10</f>
-        <v/>
+        <v>11.969832397959184</v>
       </c>
     </row>
     <row r="24">
@@ -1996,9 +2182,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="38">
         <f>I22-I19</f>
-        <v/>
+        <v>8.705332653061223</v>
       </c>
     </row>
     <row r="25">
@@ -2007,16 +2200,22 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="50" t="n"/>
       <c r="I25" s="47">
         <f>I24/I22</f>
-        <v/>
+        <v>0.7999999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:G18"/>
@@ -2026,18 +2225,27 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2046,23 +2254,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2085,7 +2293,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2168,11 +2376,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.05102040816326531</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>1.1224489795918369</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -2209,11 +2417,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.025510204081632654</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.45918367346938777</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -2250,11 +2458,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.27</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -2291,11 +2499,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.008</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -2337,11 +2545,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -2454,9 +2662,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="50" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>1.9096326530612246</v>
       </c>
     </row>
     <row r="17">
@@ -2465,12 +2680,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.19096326530612248</v>
       </c>
     </row>
     <row r="18">
@@ -2479,9 +2700,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="50" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
+        <v>2.1005959183673473</v>
       </c>
     </row>
     <row r="19"/>
@@ -2491,6 +2719,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="50" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.2</v>
       </c>
@@ -2501,9 +2735,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="50" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>10.502979591836736</v>
       </c>
     </row>
     <row r="22">
@@ -2512,9 +2753,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>11.553277551020411</v>
       </c>
     </row>
     <row r="23">
@@ -2523,9 +2771,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>8.402383673469389</v>
       </c>
     </row>
     <row r="24">
@@ -2534,9 +2789,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -2556,15 +2818,23 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2573,23 +2843,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2612,7 +2882,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2695,11 +2965,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.061224489795918366</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -2736,11 +3006,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.09473684210526316</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.7578947368421053</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -2777,11 +3047,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.024</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -2818,11 +3088,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.02666666666666667</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.05333333333333334</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -2864,11 +3134,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.075</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -2981,9 +3251,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="50" t="n"/>
       <c r="I16" s="36">
         <f>SUM(I5:I14)</f>
-        <v/>
+        <v>1.7673709273182956</v>
       </c>
     </row>
     <row r="17">
@@ -2992,12 +3269,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="50" t="n"/>
       <c r="H17" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="38">
         <f>I16*H17</f>
-        <v/>
+        <v>0.17673709273182958</v>
       </c>
     </row>
     <row r="18">
@@ -3006,9 +3289,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="50" t="n"/>
       <c r="I18" s="40">
         <f>I16+I17</f>
-        <v/>
+        <v>1.944108020050125</v>
       </c>
     </row>
     <row r="19"/>
@@ -3018,6 +3308,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="50" t="n"/>
       <c r="H20" s="42" t="n">
         <v>0.2</v>
       </c>
@@ -3028,9 +3324,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="50" t="n"/>
       <c r="I21" s="44">
         <f>I18/H20</f>
-        <v/>
+        <v>9.720540100250625</v>
       </c>
     </row>
     <row r="22">
@@ -3039,9 +3342,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
       <c r="I22" s="46">
         <f>I21*1.10</f>
-        <v/>
+        <v>10.692594110275689</v>
       </c>
     </row>
     <row r="23">
@@ -3050,9 +3360,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="38">
         <f>I21-I18</f>
-        <v/>
+        <v>7.7764320802005</v>
       </c>
     </row>
     <row r="24">
@@ -3061,9 +3378,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="47">
         <f>I23/I21</f>
-        <v/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -3083,14 +3407,22 @@
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>